--- a/Racecard_20260429_Terry.xlsx
+++ b/Racecard_20260429_Terry.xlsx
@@ -665,35 +665,35 @@
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>14.42</v>
+        <v>14.371</v>
       </c>
       <c r="U2" t="n">
-        <v>23.121</v>
+        <v>23.042</v>
       </c>
       <c r="V2" t="n">
-        <v>23.917</v>
+        <v>23.836</v>
       </c>
       <c r="W2" t="n">
-        <v>23.932</v>
+        <v>23.851</v>
       </c>
       <c r="X2" t="n">
-        <v>23.978</v>
+        <v>23.896</v>
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>37.541</v>
+        <v>37.413</v>
       </c>
       <c r="AA2" t="n">
-        <v>47.91</v>
+        <v>47.747</v>
       </c>
       <c r="AB2" t="n">
-        <v>47.91</v>
+        <v>47.747</v>
       </c>
       <c r="AC2" t="n">
-        <v>109.368</v>
+        <v>108.996</v>
       </c>
       <c r="AD2" t="n">
-        <v>46.39</v>
+        <v>43.9</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -785,35 +785,35 @@
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>14.662</v>
+        <v>14.613</v>
       </c>
       <c r="U3" t="n">
-        <v>23.599</v>
+        <v>23.519</v>
       </c>
       <c r="V3" t="n">
-        <v>24.271</v>
+        <v>24.19</v>
       </c>
       <c r="W3" t="n">
-        <v>24.041</v>
+        <v>23.96</v>
       </c>
       <c r="X3" t="n">
-        <v>23.874</v>
+        <v>23.794</v>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>38.261</v>
+        <v>38.132</v>
       </c>
       <c r="AA3" t="n">
-        <v>47.915</v>
+        <v>47.754</v>
       </c>
       <c r="AB3" t="n">
-        <v>47.915</v>
+        <v>47.754</v>
       </c>
       <c r="AC3" t="n">
-        <v>110.447</v>
+        <v>110.076</v>
       </c>
       <c r="AD3" t="n">
-        <v>17.29</v>
+        <v>16.3</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -905,35 +905,35 @@
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
-        <v>14.133</v>
+        <v>14.085</v>
       </c>
       <c r="U4" t="n">
-        <v>24.059</v>
+        <v>23.977</v>
       </c>
       <c r="V4" t="n">
-        <v>24.491</v>
+        <v>24.409</v>
       </c>
       <c r="W4" t="n">
-        <v>24.24</v>
+        <v>24.158</v>
       </c>
       <c r="X4" t="n">
-        <v>23.867</v>
+        <v>23.787</v>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>38.192</v>
+        <v>38.062</v>
       </c>
       <c r="AA4" t="n">
-        <v>48.107</v>
+        <v>47.945</v>
       </c>
       <c r="AB4" t="n">
-        <v>48.107</v>
+        <v>47.945</v>
       </c>
       <c r="AC4" t="n">
-        <v>110.79</v>
+        <v>110.416</v>
       </c>
       <c r="AD4" t="n">
-        <v>12.63</v>
+        <v>11.94</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -1025,35 +1025,35 @@
       </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>14.387</v>
+        <v>14.338</v>
       </c>
       <c r="U5" t="n">
-        <v>23.147</v>
+        <v>23.068</v>
       </c>
       <c r="V5" t="n">
-        <v>24.604</v>
+        <v>24.52</v>
       </c>
       <c r="W5" t="n">
-        <v>24.732</v>
+        <v>24.648</v>
       </c>
       <c r="X5" t="n">
-        <v>24.011</v>
+        <v>23.929</v>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>37.534</v>
+        <v>37.406</v>
       </c>
       <c r="AA5" t="n">
-        <v>48.743</v>
+        <v>48.577</v>
       </c>
       <c r="AB5" t="n">
-        <v>48.743</v>
+        <v>48.577</v>
       </c>
       <c r="AC5" t="n">
-        <v>110.881</v>
+        <v>110.503</v>
       </c>
       <c r="AD5" t="n">
-        <v>11.62</v>
+        <v>11.02</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1145,35 +1145,35 @@
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="n">
-        <v>13.949</v>
+        <v>13.901</v>
       </c>
       <c r="U6" t="n">
-        <v>23.236</v>
+        <v>23.157</v>
       </c>
       <c r="V6" t="n">
-        <v>24.595</v>
+        <v>24.512</v>
       </c>
       <c r="W6" t="n">
-        <v>24.911</v>
+        <v>24.827</v>
       </c>
       <c r="X6" t="n">
-        <v>24.359</v>
+        <v>24.276</v>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
-        <v>37.185</v>
+        <v>37.058</v>
       </c>
       <c r="AA6" t="n">
-        <v>49.27</v>
+        <v>49.103</v>
       </c>
       <c r="AB6" t="n">
-        <v>49.27</v>
+        <v>49.103</v>
       </c>
       <c r="AC6" t="n">
-        <v>111.05</v>
+        <v>110.673</v>
       </c>
       <c r="AD6" t="n">
-        <v>9.960000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1265,35 +1265,35 @@
       </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="n">
-        <v>13.912</v>
+        <v>13.865</v>
       </c>
       <c r="U7" t="n">
-        <v>23.822</v>
+        <v>23.742</v>
       </c>
       <c r="V7" t="n">
-        <v>24.483</v>
+        <v>24.401</v>
       </c>
       <c r="W7" t="n">
-        <v>24.777</v>
+        <v>24.694</v>
       </c>
       <c r="X7" t="n">
-        <v>25.747</v>
+        <v>25.66</v>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
-        <v>37.734</v>
+        <v>37.607</v>
       </c>
       <c r="AA7" t="n">
-        <v>50.524</v>
+        <v>50.354</v>
       </c>
       <c r="AB7" t="n">
-        <v>50.524</v>
+        <v>50.354</v>
       </c>
       <c r="AC7" t="n">
-        <v>112.741</v>
+        <v>112.362</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1378,7 +1378,9 @@
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
+      <c r="AD8" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
@@ -1450,7 +1452,9 @@
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
+      <c r="AD9" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
@@ -1522,7 +1526,9 @@
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
+      <c r="AD10" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
@@ -1594,7 +1600,9 @@
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
+      <c r="AD11" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
@@ -1666,7 +1674,9 @@
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
+      <c r="AD12" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
@@ -1738,7 +1748,9 @@
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
+      <c r="AD13" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
@@ -1999,31 +2011,31 @@
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>23.513</v>
+        <v>23.433</v>
       </c>
       <c r="U2" t="n">
-        <v>22.848</v>
+        <v>22.77</v>
       </c>
       <c r="V2" t="n">
-        <v>23.651</v>
+        <v>23.571</v>
       </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>46.361</v>
+        <v>46.203</v>
       </c>
       <c r="AA2" t="n">
-        <v>46.499</v>
+        <v>46.341</v>
       </c>
       <c r="AB2" t="n">
-        <v>46.499</v>
+        <v>46.341</v>
       </c>
       <c r="AC2" t="n">
-        <v>70.012</v>
+        <v>69.774</v>
       </c>
       <c r="AD2" t="n">
-        <v>34.72</v>
+        <v>34.08</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -2111,31 +2123,31 @@
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>24.132</v>
+        <v>24.051</v>
       </c>
       <c r="U3" t="n">
-        <v>22.8</v>
+        <v>22.724</v>
       </c>
       <c r="V3" t="n">
-        <v>23.324</v>
+        <v>23.245</v>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>46.932</v>
+        <v>46.775</v>
       </c>
       <c r="AA3" t="n">
-        <v>46.124</v>
+        <v>45.969</v>
       </c>
       <c r="AB3" t="n">
-        <v>46.124</v>
+        <v>45.969</v>
       </c>
       <c r="AC3" t="n">
-        <v>70.256</v>
+        <v>70.02</v>
       </c>
       <c r="AD3" t="n">
-        <v>22.29</v>
+        <v>21.77</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -2223,31 +2235,31 @@
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
-        <v>24.399</v>
+        <v>24.316</v>
       </c>
       <c r="U4" t="n">
-        <v>22.917</v>
+        <v>22.839</v>
       </c>
       <c r="V4" t="n">
-        <v>23.241</v>
+        <v>23.162</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>47.316</v>
+        <v>47.155</v>
       </c>
       <c r="AA4" t="n">
-        <v>46.158</v>
+        <v>46.001</v>
       </c>
       <c r="AB4" t="n">
-        <v>46.158</v>
+        <v>46.001</v>
       </c>
       <c r="AC4" t="n">
-        <v>70.557</v>
+        <v>70.31699999999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>12.9</v>
+        <v>12.68</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -2335,31 +2347,31 @@
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>23.924</v>
+        <v>23.843</v>
       </c>
       <c r="U5" t="n">
-        <v>22.996</v>
+        <v>22.918</v>
       </c>
       <c r="V5" t="n">
-        <v>23.746</v>
+        <v>23.666</v>
       </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>46.92</v>
+        <v>46.761</v>
       </c>
       <c r="AA5" t="n">
-        <v>46.742</v>
+        <v>46.584</v>
       </c>
       <c r="AB5" t="n">
-        <v>46.742</v>
+        <v>46.584</v>
       </c>
       <c r="AC5" t="n">
-        <v>70.666</v>
+        <v>70.42700000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>10.59</v>
+        <v>10.38</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -2447,31 +2459,31 @@
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="n">
-        <v>24.928</v>
+        <v>24.844</v>
       </c>
       <c r="U6" t="n">
-        <v>22.892</v>
+        <v>22.814</v>
       </c>
       <c r="V6" t="n">
-        <v>23.168</v>
+        <v>23.089</v>
       </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
-        <v>47.82</v>
+        <v>47.658</v>
       </c>
       <c r="AA6" t="n">
-        <v>46.06</v>
+        <v>45.903</v>
       </c>
       <c r="AB6" t="n">
-        <v>46.06</v>
+        <v>45.903</v>
       </c>
       <c r="AC6" t="n">
-        <v>70.988</v>
+        <v>70.747</v>
       </c>
       <c r="AD6" t="n">
-        <v>5.9</v>
+        <v>5.79</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -2559,31 +2571,31 @@
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="n">
-        <v>23.917</v>
+        <v>23.836</v>
       </c>
       <c r="U7" t="n">
-        <v>22.949</v>
+        <v>22.872</v>
       </c>
       <c r="V7" t="n">
-        <v>24.215</v>
+        <v>24.133</v>
       </c>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
-        <v>46.866</v>
+        <v>46.708</v>
       </c>
       <c r="AA7" t="n">
-        <v>47.164</v>
+        <v>47.005</v>
       </c>
       <c r="AB7" t="n">
-        <v>47.164</v>
+        <v>47.005</v>
       </c>
       <c r="AC7" t="n">
-        <v>71.081</v>
+        <v>70.84099999999999</v>
       </c>
       <c r="AD7" t="n">
-        <v>4.98</v>
+        <v>4.88</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -2671,31 +2683,31 @@
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="n">
-        <v>24.322</v>
+        <v>24.24</v>
       </c>
       <c r="U8" t="n">
-        <v>23.058</v>
+        <v>22.981</v>
       </c>
       <c r="V8" t="n">
-        <v>23.79</v>
+        <v>23.709</v>
       </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="n">
-        <v>47.38</v>
+        <v>47.221</v>
       </c>
       <c r="AA8" t="n">
-        <v>46.848</v>
+        <v>46.69</v>
       </c>
       <c r="AB8" t="n">
-        <v>46.848</v>
+        <v>46.69</v>
       </c>
       <c r="AC8" t="n">
-        <v>71.17</v>
+        <v>70.93000000000001</v>
       </c>
       <c r="AD8" t="n">
-        <v>4.24</v>
+        <v>4.15</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -2783,31 +2795,31 @@
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="n">
-        <v>24.744</v>
+        <v>24.661</v>
       </c>
       <c r="U9" t="n">
-        <v>22.906</v>
+        <v>22.829</v>
       </c>
       <c r="V9" t="n">
-        <v>23.733</v>
+        <v>23.653</v>
       </c>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="n">
-        <v>47.65</v>
+        <v>47.49</v>
       </c>
       <c r="AA9" t="n">
-        <v>46.639</v>
+        <v>46.482</v>
       </c>
       <c r="AB9" t="n">
-        <v>46.639</v>
+        <v>46.482</v>
       </c>
       <c r="AC9" t="n">
-        <v>71.383</v>
+        <v>71.143</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -2895,31 +2907,31 @@
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="n">
-        <v>24.778</v>
+        <v>24.694</v>
       </c>
       <c r="U10" t="n">
-        <v>22.99</v>
+        <v>22.912</v>
       </c>
       <c r="V10" t="n">
-        <v>23.975</v>
+        <v>23.894</v>
       </c>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="n">
-        <v>47.768</v>
+        <v>47.606</v>
       </c>
       <c r="AA10" t="n">
-        <v>46.965</v>
+        <v>46.806</v>
       </c>
       <c r="AB10" t="n">
-        <v>46.965</v>
+        <v>46.806</v>
       </c>
       <c r="AC10" t="n">
-        <v>71.74299999999999</v>
+        <v>71.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -3000,7 +3012,9 @@
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
+      <c r="AD11" t="n">
+        <v>0.66</v>
+      </c>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
@@ -3072,7 +3086,9 @@
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
+      <c r="AD12" t="n">
+        <v>0.66</v>
+      </c>
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
@@ -3104,7 +3120,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>潘明輝</t>
+          <t>楊明綸</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3112,7 +3128,11 @@
           <t>呂健威</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>21%(3/14)</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>52</v>
       </c>
@@ -3140,7 +3160,9 @@
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
+      <c r="AD13" t="n">
+        <v>0.66</v>
+      </c>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
@@ -3407,37 +3429,37 @@
         <v>24.06</v>
       </c>
       <c r="T2" t="n">
-        <v>15.129</v>
+        <v>15.078</v>
       </c>
       <c r="U2" t="n">
-        <v>24.027</v>
+        <v>23.946</v>
       </c>
       <c r="V2" t="n">
-        <v>24.68</v>
+        <v>24.597</v>
       </c>
       <c r="W2" t="n">
-        <v>24.281</v>
+        <v>24.2</v>
       </c>
       <c r="X2" t="n">
-        <v>24.302</v>
+        <v>24.22</v>
       </c>
       <c r="Y2" t="n">
-        <v>24.292</v>
+        <v>24.21</v>
       </c>
       <c r="Z2" t="n">
-        <v>39.156</v>
+        <v>39.024</v>
       </c>
       <c r="AA2" t="n">
-        <v>48.594</v>
+        <v>48.43</v>
       </c>
       <c r="AB2" t="n">
-        <v>48.594</v>
+        <v>48.43</v>
       </c>
       <c r="AC2" t="n">
-        <v>136.711</v>
+        <v>136.251</v>
       </c>
       <c r="AD2" t="n">
-        <v>23.27</v>
+        <v>22.63</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -3531,37 +3553,37 @@
         <v>24.13</v>
       </c>
       <c r="T3" t="n">
-        <v>15.1</v>
+        <v>15.048</v>
       </c>
       <c r="U3" t="n">
-        <v>24.149</v>
+        <v>24.067</v>
       </c>
       <c r="V3" t="n">
-        <v>24.911</v>
+        <v>24.826</v>
       </c>
       <c r="W3" t="n">
-        <v>24.35</v>
+        <v>24.267</v>
       </c>
       <c r="X3" t="n">
-        <v>24.12</v>
+        <v>24.038</v>
       </c>
       <c r="Y3" t="n">
-        <v>24.11</v>
+        <v>24.028</v>
       </c>
       <c r="Z3" t="n">
-        <v>39.249</v>
+        <v>39.115</v>
       </c>
       <c r="AA3" t="n">
-        <v>48.23</v>
+        <v>48.066</v>
       </c>
       <c r="AB3" t="n">
-        <v>48.23</v>
+        <v>48.066</v>
       </c>
       <c r="AC3" t="n">
-        <v>136.74</v>
+        <v>136.274</v>
       </c>
       <c r="AD3" t="n">
-        <v>22.52</v>
+        <v>22.06</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -3655,37 +3677,37 @@
         <v>24.751</v>
       </c>
       <c r="T4" t="n">
-        <v>15.125</v>
+        <v>15.074</v>
       </c>
       <c r="U4" t="n">
-        <v>23.902</v>
+        <v>23.821</v>
       </c>
       <c r="V4" t="n">
-        <v>24.518</v>
+        <v>24.435</v>
       </c>
       <c r="W4" t="n">
-        <v>24.237</v>
+        <v>24.154</v>
       </c>
       <c r="X4" t="n">
-        <v>24.603</v>
+        <v>24.519</v>
       </c>
       <c r="Y4" t="n">
-        <v>24.862</v>
+        <v>24.777</v>
       </c>
       <c r="Z4" t="n">
-        <v>39.027</v>
+        <v>38.895</v>
       </c>
       <c r="AA4" t="n">
-        <v>49.465</v>
+        <v>49.296</v>
       </c>
       <c r="AB4" t="n">
-        <v>49.465</v>
+        <v>49.296</v>
       </c>
       <c r="AC4" t="n">
-        <v>137.247</v>
+        <v>136.78</v>
       </c>
       <c r="AD4" t="n">
-        <v>12.73</v>
+        <v>12.48</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -3721,99 +3743,99 @@
         <v>2200</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>夢照發</t>
+          <t>清雲龍駒</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>巴度</t>
+          <t>奧爾民</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>黎昭昇</t>
+          <t>賀賢</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>35%(7/20)</t>
+          <t>26%(8/31)</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="J5" t="n">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="K5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2.15.75</t>
+          <t>2.15.47</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>14.63</v>
+        <v>14.498</v>
       </c>
       <c r="O5" t="n">
-        <v>23.877</v>
+        <v>23.51</v>
       </c>
       <c r="P5" t="n">
-        <v>24.707</v>
+        <v>24.684</v>
       </c>
       <c r="Q5" t="n">
-        <v>24.647</v>
+        <v>24.613</v>
       </c>
       <c r="R5" t="n">
-        <v>24.593</v>
+        <v>24.383</v>
       </c>
       <c r="S5" t="n">
-        <v>24.683</v>
+        <v>24.313</v>
       </c>
       <c r="T5" t="n">
-        <v>14.955</v>
+        <v>14.815</v>
       </c>
       <c r="U5" t="n">
-        <v>24.038</v>
+        <v>23.692</v>
       </c>
       <c r="V5" t="n">
-        <v>24.727</v>
+        <v>24.756</v>
       </c>
       <c r="W5" t="n">
-        <v>24.59</v>
+        <v>24.738</v>
       </c>
       <c r="X5" t="n">
-        <v>24.535</v>
+        <v>24.507</v>
       </c>
       <c r="Y5" t="n">
-        <v>24.626</v>
+        <v>24.437</v>
       </c>
       <c r="Z5" t="n">
-        <v>38.993</v>
+        <v>38.507</v>
       </c>
       <c r="AA5" t="n">
-        <v>49.161</v>
+        <v>48.944</v>
       </c>
       <c r="AB5" t="n">
-        <v>49.161</v>
+        <v>48.944</v>
       </c>
       <c r="AC5" t="n">
-        <v>137.471</v>
+        <v>136.945</v>
       </c>
       <c r="AD5" t="n">
-        <v>9.9</v>
+        <v>10.37</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>3-2-3-3-4-4</t>
+          <t>1-1-1-3-5-4</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -3823,12 +3845,12 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>外疊搶放 (外檔, 頭段排名2)</t>
+          <t>外疊搶放 (外檔, 頭段排名1)</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2022_H168</t>
+          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2024_K160</t>
         </is>
       </c>
     </row>
@@ -3845,99 +3867,99 @@
         <v>2200</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>清雲龍駒</t>
+          <t>夢照發</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>潘明輝</t>
+          <t>巴度</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>賀賢</t>
+          <t>黎昭昇</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>22%(7/32)</t>
+          <t>35%(7/20)</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="J6" t="n">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="K6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2.15.47</t>
+          <t>2.15.75</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>14.498</v>
+        <v>14.63</v>
       </c>
       <c r="O6" t="n">
-        <v>23.51</v>
+        <v>23.877</v>
       </c>
       <c r="P6" t="n">
-        <v>24.684</v>
+        <v>24.707</v>
       </c>
       <c r="Q6" t="n">
-        <v>24.613</v>
+        <v>24.647</v>
       </c>
       <c r="R6" t="n">
-        <v>24.383</v>
+        <v>24.593</v>
       </c>
       <c r="S6" t="n">
-        <v>24.313</v>
+        <v>24.683</v>
       </c>
       <c r="T6" t="n">
-        <v>14.877</v>
+        <v>14.904</v>
       </c>
       <c r="U6" t="n">
-        <v>23.791</v>
+        <v>23.956</v>
       </c>
       <c r="V6" t="n">
-        <v>24.859</v>
+        <v>24.643</v>
       </c>
       <c r="W6" t="n">
-        <v>24.841</v>
+        <v>24.506</v>
       </c>
       <c r="X6" t="n">
-        <v>24.61</v>
+        <v>24.452</v>
       </c>
       <c r="Y6" t="n">
-        <v>24.539</v>
+        <v>24.542</v>
       </c>
       <c r="Z6" t="n">
-        <v>38.668</v>
+        <v>38.86</v>
       </c>
       <c r="AA6" t="n">
-        <v>49.149</v>
+        <v>48.994</v>
       </c>
       <c r="AB6" t="n">
-        <v>49.149</v>
+        <v>48.994</v>
       </c>
       <c r="AC6" t="n">
-        <v>137.517</v>
+        <v>137.003</v>
       </c>
       <c r="AD6" t="n">
-        <v>9.4</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1-1-1-4-5-5</t>
+          <t>3-2-3-4-4-5</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -3947,12 +3969,12 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>外疊搶放 (外檔, 頭段排名1)</t>
+          <t>外疊搶放 (外檔, 頭段排名2)</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2024_K160</t>
+          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2022_H168</t>
         </is>
       </c>
     </row>
@@ -4027,37 +4049,37 @@
         <v>24.099</v>
       </c>
       <c r="T7" t="n">
-        <v>15.301</v>
+        <v>15.25</v>
       </c>
       <c r="U7" t="n">
-        <v>23.991</v>
+        <v>23.91</v>
       </c>
       <c r="V7" t="n">
-        <v>24.979</v>
+        <v>24.895</v>
       </c>
       <c r="W7" t="n">
-        <v>24.719</v>
+        <v>24.636</v>
       </c>
       <c r="X7" t="n">
-        <v>24.449</v>
+        <v>24.366</v>
       </c>
       <c r="Y7" t="n">
-        <v>24.15</v>
+        <v>24.068</v>
       </c>
       <c r="Z7" t="n">
-        <v>39.292</v>
+        <v>39.16</v>
       </c>
       <c r="AA7" t="n">
-        <v>48.599</v>
+        <v>48.434</v>
       </c>
       <c r="AB7" t="n">
-        <v>48.599</v>
+        <v>48.434</v>
       </c>
       <c r="AC7" t="n">
-        <v>137.589</v>
+        <v>137.125</v>
       </c>
       <c r="AD7" t="n">
-        <v>8.67</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -4151,37 +4173,37 @@
         <v>24.58</v>
       </c>
       <c r="T8" t="n">
-        <v>14.946</v>
+        <v>14.895</v>
       </c>
       <c r="U8" t="n">
-        <v>24.777</v>
+        <v>24.693</v>
       </c>
       <c r="V8" t="n">
-        <v>24.373</v>
+        <v>24.291</v>
       </c>
       <c r="W8" t="n">
-        <v>24.653</v>
+        <v>24.57</v>
       </c>
       <c r="X8" t="n">
-        <v>24.443</v>
+        <v>24.36</v>
       </c>
       <c r="Y8" t="n">
-        <v>24.633</v>
+        <v>24.55</v>
       </c>
       <c r="Z8" t="n">
-        <v>39.723</v>
+        <v>39.588</v>
       </c>
       <c r="AA8" t="n">
-        <v>49.076</v>
+        <v>48.91</v>
       </c>
       <c r="AB8" t="n">
-        <v>49.076</v>
+        <v>48.91</v>
       </c>
       <c r="AC8" t="n">
-        <v>137.825</v>
+        <v>137.359</v>
       </c>
       <c r="AD8" t="n">
-        <v>6.65</v>
+        <v>6.51</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -4275,37 +4297,37 @@
         <v>24.235</v>
       </c>
       <c r="T9" t="n">
-        <v>14.983</v>
+        <v>14.932</v>
       </c>
       <c r="U9" t="n">
-        <v>24.369</v>
+        <v>24.287</v>
       </c>
       <c r="V9" t="n">
-        <v>24.652</v>
+        <v>24.569</v>
       </c>
       <c r="W9" t="n">
-        <v>24.655</v>
+        <v>24.572</v>
       </c>
       <c r="X9" t="n">
-        <v>24.781</v>
+        <v>24.697</v>
       </c>
       <c r="Y9" t="n">
-        <v>24.463</v>
+        <v>24.381</v>
       </c>
       <c r="Z9" t="n">
-        <v>39.352</v>
+        <v>39.219</v>
       </c>
       <c r="AA9" t="n">
-        <v>49.244</v>
+        <v>49.078</v>
       </c>
       <c r="AB9" t="n">
-        <v>49.244</v>
+        <v>49.078</v>
       </c>
       <c r="AC9" t="n">
-        <v>137.903</v>
+        <v>137.438</v>
       </c>
       <c r="AD9" t="n">
-        <v>6.09</v>
+        <v>5.95</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -4399,37 +4421,37 @@
         <v>24.75</v>
       </c>
       <c r="T10" t="n">
-        <v>15.142</v>
+        <v>15.091</v>
       </c>
       <c r="U10" t="n">
-        <v>24.771</v>
+        <v>24.687</v>
       </c>
       <c r="V10" t="n">
-        <v>25.546</v>
+        <v>25.46</v>
       </c>
       <c r="W10" t="n">
-        <v>25.564</v>
+        <v>25.478</v>
       </c>
       <c r="X10" t="n">
-        <v>23.812</v>
+        <v>23.731</v>
       </c>
       <c r="Y10" t="n">
-        <v>24.89</v>
+        <v>24.805</v>
       </c>
       <c r="Z10" t="n">
-        <v>39.913</v>
+        <v>39.778</v>
       </c>
       <c r="AA10" t="n">
-        <v>48.702</v>
+        <v>48.536</v>
       </c>
       <c r="AB10" t="n">
-        <v>48.702</v>
+        <v>48.536</v>
       </c>
       <c r="AC10" t="n">
-        <v>139.725</v>
+        <v>139.252</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -4514,7 +4536,9 @@
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
+      <c r="AD11" t="n">
+        <v>0.35</v>
+      </c>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
@@ -4586,7 +4610,9 @@
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
+      <c r="AD12" t="n">
+        <v>0.35</v>
+      </c>
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
@@ -4658,7 +4684,9 @@
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
+      <c r="AD13" t="n">
+        <v>0.35</v>
+      </c>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
@@ -4919,31 +4947,31 @@
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>24.053</v>
+        <v>23.984</v>
       </c>
       <c r="U2" t="n">
-        <v>22.408</v>
+        <v>22.343</v>
       </c>
       <c r="V2" t="n">
-        <v>22.826</v>
+        <v>22.76</v>
       </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>46.461</v>
+        <v>46.327</v>
       </c>
       <c r="AA2" t="n">
-        <v>45.234</v>
+        <v>45.103</v>
       </c>
       <c r="AB2" t="n">
-        <v>45.234</v>
+        <v>45.103</v>
       </c>
       <c r="AC2" t="n">
-        <v>69.28700000000001</v>
+        <v>69.087</v>
       </c>
       <c r="AD2" t="n">
-        <v>40.13</v>
+        <v>40.6</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -5031,31 +5059,31 @@
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>24.581</v>
+        <v>24.497</v>
       </c>
       <c r="U3" t="n">
-        <v>22.1</v>
+        <v>22.025</v>
       </c>
       <c r="V3" t="n">
-        <v>23.149</v>
+        <v>23.07</v>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>46.681</v>
+        <v>46.522</v>
       </c>
       <c r="AA3" t="n">
-        <v>45.249</v>
+        <v>45.095</v>
       </c>
       <c r="AB3" t="n">
-        <v>45.249</v>
+        <v>45.095</v>
       </c>
       <c r="AC3" t="n">
-        <v>69.83</v>
+        <v>69.592</v>
       </c>
       <c r="AD3" t="n">
-        <v>16.88</v>
+        <v>17.89</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -5143,35 +5171,35 @@
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
-        <v>24.377</v>
+        <v>24.294</v>
       </c>
       <c r="U4" t="n">
-        <v>22.681</v>
+        <v>22.604</v>
       </c>
       <c r="V4" t="n">
-        <v>23.101</v>
+        <v>23.023</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>47.058</v>
+        <v>46.898</v>
       </c>
       <c r="AA4" t="n">
-        <v>45.782</v>
+        <v>45.627</v>
       </c>
       <c r="AB4" t="n">
-        <v>45.782</v>
+        <v>45.627</v>
       </c>
       <c r="AC4" t="n">
-        <v>70.15900000000001</v>
+        <v>69.92100000000001</v>
       </c>
       <c r="AD4" t="n">
-        <v>9.98</v>
+        <v>10.48</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5-6-3</t>
+          <t>4-5-3</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -5181,7 +5209,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>中置守位 (中檔, 頭段排名6)</t>
+          <t>中置守位 (中檔, 頭段排名5)</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -5255,31 +5283,31 @@
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>23.945</v>
+        <v>23.864</v>
       </c>
       <c r="U5" t="n">
-        <v>22.497</v>
+        <v>22.421</v>
       </c>
       <c r="V5" t="n">
-        <v>23.862</v>
+        <v>23.782</v>
       </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>46.442</v>
+        <v>46.285</v>
       </c>
       <c r="AA5" t="n">
-        <v>46.359</v>
+        <v>46.203</v>
       </c>
       <c r="AB5" t="n">
-        <v>46.359</v>
+        <v>46.203</v>
       </c>
       <c r="AC5" t="n">
-        <v>70.304</v>
+        <v>70.06699999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>7.92</v>
+        <v>8.27</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -5315,102 +5343,102 @@
         <v>1200</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>悠然常勝</t>
+          <t>紅愛舍</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>布浩榮</t>
+          <t>布文</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>巫偉傑</t>
+          <t>韋達</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>100%(2/2)</t>
+          <t>15%(2/13)</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="J6" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="K6" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1.10.39</t>
+          <t>1.09.26</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>24.375</v>
+        <v>24.384</v>
       </c>
       <c r="O6" t="n">
-        <v>22.726</v>
+        <v>22.552</v>
       </c>
       <c r="P6" t="n">
-        <v>23.711</v>
+        <v>23.166</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="n">
-        <v>24.326</v>
+        <v>24.381</v>
       </c>
       <c r="U6" t="n">
-        <v>22.55</v>
+        <v>22.625</v>
       </c>
       <c r="V6" t="n">
-        <v>23.437</v>
+        <v>23.285</v>
       </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
-        <v>46.876</v>
+        <v>47.006</v>
       </c>
       <c r="AA6" t="n">
-        <v>45.987</v>
+        <v>45.91</v>
       </c>
       <c r="AB6" t="n">
-        <v>45.987</v>
+        <v>45.91</v>
       </c>
       <c r="AC6" t="n">
-        <v>70.313</v>
+        <v>70.291</v>
       </c>
       <c r="AD6" t="n">
-        <v>7.81</v>
+        <v>5.75</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4-5-5</t>
+          <t>5-7-5</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>中置守位</t>
+          <t>包廂跟前</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>中置守位 (外檔, 頭段排名5)</t>
+          <t>包廂跟前 (內檔, 頭段排名7)</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2025_L136</t>
+          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2022_H110</t>
         </is>
       </c>
     </row>
@@ -5427,102 +5455,102 @@
         <v>1200</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>紅愛舍</t>
+          <t>悠然常勝</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>布文</t>
+          <t>布浩榮</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>韋達</t>
+          <t>巫偉傑</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>15%(2/13)</t>
+          <t>100%(2/2)</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="J7" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1.09.26</t>
+          <t>1.10.39</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>24.384</v>
+        <v>24.375</v>
       </c>
       <c r="O7" t="n">
-        <v>22.552</v>
+        <v>22.726</v>
       </c>
       <c r="P7" t="n">
-        <v>23.166</v>
+        <v>23.711</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="n">
-        <v>24.463</v>
+        <v>24.39</v>
       </c>
       <c r="U7" t="n">
-        <v>22.702</v>
+        <v>22.609</v>
       </c>
       <c r="V7" t="n">
-        <v>23.364</v>
+        <v>23.499</v>
       </c>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
-        <v>47.165</v>
+        <v>46.999</v>
       </c>
       <c r="AA7" t="n">
-        <v>46.066</v>
+        <v>46.108</v>
       </c>
       <c r="AB7" t="n">
-        <v>46.066</v>
+        <v>46.108</v>
       </c>
       <c r="AC7" t="n">
-        <v>70.529</v>
+        <v>70.498</v>
       </c>
       <c r="AD7" t="n">
-        <v>5.53</v>
+        <v>4.11</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>6-7-6</t>
+          <t>6-6-6</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>包廂跟前</t>
+          <t>中置守位</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>包廂跟前 (內檔, 頭段排名7)</t>
+          <t>中置守位 (外檔, 頭段排名6)</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2022_H110</t>
+          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2025_L136</t>
         </is>
       </c>
     </row>
@@ -5591,31 +5619,31 @@
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="n">
-        <v>24.747</v>
+        <v>24.664</v>
       </c>
       <c r="U8" t="n">
-        <v>23.054</v>
+        <v>22.976</v>
       </c>
       <c r="V8" t="n">
-        <v>23.016</v>
+        <v>22.938</v>
       </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="n">
-        <v>47.801</v>
+        <v>47.64</v>
       </c>
       <c r="AA8" t="n">
-        <v>46.07</v>
+        <v>45.914</v>
       </c>
       <c r="AB8" t="n">
-        <v>46.07</v>
+        <v>45.914</v>
       </c>
       <c r="AC8" t="n">
-        <v>70.81699999999999</v>
+        <v>70.578</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.49</v>
+        <v>3.61</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -5703,31 +5731,31 @@
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="n">
-        <v>23.768</v>
+        <v>23.688</v>
       </c>
       <c r="U9" t="n">
-        <v>22.817</v>
+        <v>22.739</v>
       </c>
       <c r="V9" t="n">
-        <v>24.482</v>
+        <v>24.399</v>
       </c>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="n">
-        <v>46.585</v>
+        <v>46.427</v>
       </c>
       <c r="AA9" t="n">
-        <v>47.299</v>
+        <v>47.138</v>
       </c>
       <c r="AB9" t="n">
-        <v>47.299</v>
+        <v>47.138</v>
       </c>
       <c r="AC9" t="n">
-        <v>71.06699999999999</v>
+        <v>70.82599999999999</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -5815,31 +5843,31 @@
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="n">
-        <v>24.512</v>
+        <v>24.429</v>
       </c>
       <c r="U10" t="n">
-        <v>22.948</v>
+        <v>22.87</v>
       </c>
       <c r="V10" t="n">
-        <v>23.618</v>
+        <v>23.538</v>
       </c>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="n">
-        <v>47.46</v>
+        <v>47.299</v>
       </c>
       <c r="AA10" t="n">
-        <v>46.566</v>
+        <v>46.408</v>
       </c>
       <c r="AB10" t="n">
-        <v>46.566</v>
+        <v>46.408</v>
       </c>
       <c r="AC10" t="n">
-        <v>71.078</v>
+        <v>70.837</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -5927,31 +5955,31 @@
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="n">
-        <v>24.577</v>
+        <v>24.494</v>
       </c>
       <c r="U11" t="n">
-        <v>23.085</v>
+        <v>23.007</v>
       </c>
       <c r="V11" t="n">
-        <v>23.562</v>
+        <v>23.482</v>
       </c>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="n">
-        <v>47.662</v>
+        <v>47.501</v>
       </c>
       <c r="AA11" t="n">
-        <v>46.647</v>
+        <v>46.489</v>
       </c>
       <c r="AB11" t="n">
-        <v>46.647</v>
+        <v>46.489</v>
       </c>
       <c r="AC11" t="n">
-        <v>71.224</v>
+        <v>70.983</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -6039,31 +6067,31 @@
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="n">
-        <v>24.692</v>
+        <v>24.608</v>
       </c>
       <c r="U12" t="n">
-        <v>22.834</v>
+        <v>22.757</v>
       </c>
       <c r="V12" t="n">
-        <v>23.715</v>
+        <v>23.635</v>
       </c>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="n">
-        <v>47.526</v>
+        <v>47.365</v>
       </c>
       <c r="AA12" t="n">
-        <v>46.549</v>
+        <v>46.392</v>
       </c>
       <c r="AB12" t="n">
-        <v>46.549</v>
+        <v>46.392</v>
       </c>
       <c r="AC12" t="n">
-        <v>71.241</v>
+        <v>71</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -6148,7 +6176,9 @@
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
+      <c r="AD13" t="n">
+        <v>0.82</v>
+      </c>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
@@ -6409,31 +6439,31 @@
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>24.271</v>
+        <v>24.188</v>
       </c>
       <c r="U2" t="n">
-        <v>22.631</v>
+        <v>22.555</v>
       </c>
       <c r="V2" t="n">
-        <v>23.527</v>
+        <v>23.447</v>
       </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>46.902</v>
+        <v>46.743</v>
       </c>
       <c r="AA2" t="n">
-        <v>46.158</v>
+        <v>46.002</v>
       </c>
       <c r="AB2" t="n">
-        <v>46.158</v>
+        <v>46.002</v>
       </c>
       <c r="AC2" t="n">
-        <v>70.429</v>
+        <v>70.19</v>
       </c>
       <c r="AD2" t="n">
-        <v>23.53</v>
+        <v>23.07</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -6521,31 +6551,31 @@
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>24.415</v>
+        <v>24.332</v>
       </c>
       <c r="U3" t="n">
-        <v>22.845</v>
+        <v>22.768</v>
       </c>
       <c r="V3" t="n">
-        <v>23.258</v>
+        <v>23.179</v>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>47.26</v>
+        <v>47.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>46.103</v>
+        <v>45.947</v>
       </c>
       <c r="AB3" t="n">
-        <v>46.103</v>
+        <v>45.947</v>
       </c>
       <c r="AC3" t="n">
-        <v>70.518</v>
+        <v>70.279</v>
       </c>
       <c r="AD3" t="n">
-        <v>19.46</v>
+        <v>19.04</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -6633,31 +6663,31 @@
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
-        <v>24.375</v>
+        <v>24.293</v>
       </c>
       <c r="U4" t="n">
-        <v>23.144</v>
+        <v>23.065</v>
       </c>
       <c r="V4" t="n">
-        <v>23.171</v>
+        <v>23.092</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>47.519</v>
+        <v>47.358</v>
       </c>
       <c r="AA4" t="n">
-        <v>46.315</v>
+        <v>46.157</v>
       </c>
       <c r="AB4" t="n">
-        <v>46.315</v>
+        <v>46.157</v>
       </c>
       <c r="AC4" t="n">
-        <v>70.69</v>
+        <v>70.45</v>
       </c>
       <c r="AD4" t="n">
-        <v>13.49</v>
+        <v>13.18</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -6745,31 +6775,31 @@
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>24.651</v>
+        <v>24.568</v>
       </c>
       <c r="U5" t="n">
-        <v>22.49</v>
+        <v>22.414</v>
       </c>
       <c r="V5" t="n">
-        <v>23.626</v>
+        <v>23.546</v>
       </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>47.141</v>
+        <v>46.982</v>
       </c>
       <c r="AA5" t="n">
-        <v>46.116</v>
+        <v>45.96</v>
       </c>
       <c r="AB5" t="n">
-        <v>46.116</v>
+        <v>45.96</v>
       </c>
       <c r="AC5" t="n">
-        <v>70.767</v>
+        <v>70.52800000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>11.44</v>
+        <v>11.14</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -6857,31 +6887,31 @@
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="n">
-        <v>23.93</v>
+        <v>23.849</v>
       </c>
       <c r="U6" t="n">
-        <v>23.089</v>
+        <v>23.011</v>
       </c>
       <c r="V6" t="n">
-        <v>23.897</v>
+        <v>23.816</v>
       </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
-        <v>47.019</v>
+        <v>46.86</v>
       </c>
       <c r="AA6" t="n">
-        <v>46.986</v>
+        <v>46.827</v>
       </c>
       <c r="AB6" t="n">
-        <v>46.986</v>
+        <v>46.827</v>
       </c>
       <c r="AC6" t="n">
-        <v>70.916</v>
+        <v>70.676</v>
       </c>
       <c r="AD6" t="n">
-        <v>8.33</v>
+        <v>8.1</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -6969,31 +6999,31 @@
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="n">
-        <v>25.348</v>
+        <v>25.263</v>
       </c>
       <c r="U7" t="n">
-        <v>22.447</v>
+        <v>22.372</v>
       </c>
       <c r="V7" t="n">
-        <v>23.174</v>
+        <v>23.096</v>
       </c>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
-        <v>47.795</v>
+        <v>47.635</v>
       </c>
       <c r="AA7" t="n">
-        <v>45.621</v>
+        <v>45.468</v>
       </c>
       <c r="AB7" t="n">
-        <v>45.621</v>
+        <v>45.468</v>
       </c>
       <c r="AC7" t="n">
-        <v>70.96899999999999</v>
+        <v>70.73099999999999</v>
       </c>
       <c r="AD7" t="n">
-        <v>7.44</v>
+        <v>7.19</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -7029,87 +7059,83 @@
         <v>1200</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>瑰麗人生</t>
+          <t>方圓星</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>楊明綸</t>
+          <t>布浩榮</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>丁冠豪</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>30%(3/10)</t>
-        </is>
-      </c>
+          <t>羅富全</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="J8" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="K8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1.09.65</t>
+          <t>1.10.21</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>24.34</v>
+        <v>24.759</v>
       </c>
       <c r="O8" t="n">
-        <v>23.015</v>
+        <v>22.462</v>
       </c>
       <c r="P8" t="n">
-        <v>23.627</v>
+        <v>23.551</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="n">
-        <v>24.528</v>
+        <v>24.701</v>
       </c>
       <c r="U8" t="n">
-        <v>22.983</v>
+        <v>22.47</v>
       </c>
       <c r="V8" t="n">
-        <v>23.534</v>
+        <v>23.588</v>
       </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="n">
-        <v>47.511</v>
+        <v>47.171</v>
       </c>
       <c r="AA8" t="n">
-        <v>46.517</v>
+        <v>46.058</v>
       </c>
       <c r="AB8" t="n">
-        <v>46.517</v>
+        <v>46.058</v>
       </c>
       <c r="AC8" t="n">
-        <v>71.045</v>
+        <v>70.759</v>
       </c>
       <c r="AD8" t="n">
-        <v>6.33</v>
+        <v>6.77</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>5-6-7</t>
+          <t>7-5-7</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -7119,12 +7145,12 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>中置守位 (外檔, 頭段排名6)</t>
+          <t>中置守位 (中檔, 頭段排名5)</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2022_H044</t>
+          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2024_K517</t>
         </is>
       </c>
     </row>
@@ -7141,87 +7167,87 @@
         <v>1200</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>方圓星</t>
+          <t>瑰麗人生</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>潘明輝</t>
+          <t>楊明綸</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>羅富全</t>
+          <t>丁冠豪</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>22%(7/32)</t>
+          <t>30%(3/10)</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="J9" t="n">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.10.21</t>
+          <t>1.09.65</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>24.759</v>
+        <v>24.34</v>
       </c>
       <c r="O9" t="n">
-        <v>22.462</v>
+        <v>23.015</v>
       </c>
       <c r="P9" t="n">
-        <v>23.551</v>
+        <v>23.627</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="n">
-        <v>24.84</v>
+        <v>24.445</v>
       </c>
       <c r="U9" t="n">
-        <v>22.596</v>
+        <v>22.905</v>
       </c>
       <c r="V9" t="n">
-        <v>23.721</v>
+        <v>23.454</v>
       </c>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="n">
-        <v>47.436</v>
+        <v>47.35</v>
       </c>
       <c r="AA9" t="n">
-        <v>46.317</v>
+        <v>46.359</v>
       </c>
       <c r="AB9" t="n">
-        <v>46.317</v>
+        <v>46.359</v>
       </c>
       <c r="AC9" t="n">
-        <v>71.157</v>
+        <v>70.804</v>
       </c>
       <c r="AD9" t="n">
-        <v>4.98</v>
+        <v>6.15</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>8-5-8</t>
+          <t>5-6-8</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -7231,12 +7257,12 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>中置守位 (中檔, 頭段排名5)</t>
+          <t>中置守位 (外檔, 頭段排名6)</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2024_K517</t>
+          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2022_H044</t>
         </is>
       </c>
     </row>
@@ -7305,35 +7331,35 @@
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="n">
-        <v>24.836</v>
+        <v>24.753</v>
       </c>
       <c r="U10" t="n">
-        <v>22.718</v>
+        <v>22.641</v>
       </c>
       <c r="V10" t="n">
-        <v>23.67</v>
+        <v>23.59</v>
       </c>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="n">
-        <v>47.554</v>
+        <v>47.394</v>
       </c>
       <c r="AA10" t="n">
-        <v>46.388</v>
+        <v>46.231</v>
       </c>
       <c r="AB10" t="n">
-        <v>46.388</v>
+        <v>46.231</v>
       </c>
       <c r="AC10" t="n">
-        <v>71.224</v>
+        <v>70.98399999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>4.32</v>
+        <v>4.17</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>7-8-9</t>
+          <t>8-8-9</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -7417,31 +7443,31 @@
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="n">
-        <v>24.935</v>
+        <v>24.851</v>
       </c>
       <c r="U11" t="n">
-        <v>23.28</v>
+        <v>23.202</v>
       </c>
       <c r="V11" t="n">
-        <v>23.876</v>
+        <v>23.796</v>
       </c>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="n">
-        <v>48.215</v>
+        <v>48.053</v>
       </c>
       <c r="AA11" t="n">
-        <v>47.156</v>
+        <v>46.998</v>
       </c>
       <c r="AB11" t="n">
-        <v>47.156</v>
+        <v>46.998</v>
       </c>
       <c r="AC11" t="n">
-        <v>72.09099999999999</v>
+        <v>71.849</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -7526,7 +7552,9 @@
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
+      <c r="AD12" t="n">
+        <v>0.27</v>
+      </c>
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
@@ -7598,7 +7626,9 @@
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
+      <c r="AD13" t="n">
+        <v>0.27</v>
+      </c>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
@@ -7807,106 +7837,106 @@
         <v>1650</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>浪漫老撾</t>
+          <t>隨緣得勝</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>布浩榮</t>
+          <t>周俊樂 (-2)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>巫偉傑</t>
+          <t>游達榮</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>100%(2/2)</t>
+          <t>33%(5/15)</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="J2" t="n">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1.38.85</t>
+          <t>1.39.12</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>28.665</v>
+        <v>29.056</v>
       </c>
       <c r="O2" t="n">
-        <v>23.655</v>
+        <v>23.855</v>
       </c>
       <c r="P2" t="n">
-        <v>24.038</v>
+        <v>23.939</v>
       </c>
       <c r="Q2" t="n">
-        <v>24.168</v>
+        <v>23.229</v>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>28.343</v>
+        <v>28.976</v>
       </c>
       <c r="U2" t="n">
-        <v>23.433</v>
+        <v>23.827</v>
       </c>
       <c r="V2" t="n">
-        <v>23.955</v>
+        <v>23.974</v>
       </c>
       <c r="W2" t="n">
-        <v>24.084</v>
+        <v>23.264</v>
       </c>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>51.776</v>
+        <v>52.803</v>
       </c>
       <c r="AA2" t="n">
-        <v>48.039</v>
+        <v>47.238</v>
       </c>
       <c r="AB2" t="n">
-        <v>48.039</v>
+        <v>47.238</v>
       </c>
       <c r="AC2" t="n">
-        <v>99.815</v>
+        <v>100.041</v>
       </c>
       <c r="AD2" t="n">
-        <v>30.9</v>
+        <v>19.25</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2-2-1-1</t>
+          <t>9-8-8-1</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>前置貼欄</t>
+          <t>留後追趕</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>前置貼欄 (內檔, 頭段排名2)</t>
+          <t>留後追趕 (中檔, 頭段排名8)</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2021_G476</t>
+          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2024_K223</t>
         </is>
       </c>
     </row>
@@ -7923,106 +7953,106 @@
         <v>1650</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>隨緣得勝</t>
+          <t>浪漫老撾</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>周俊樂 (-2)</t>
+          <t>布浩榮</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>游達榮</t>
+          <t>巫偉傑</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>33%(5/15)</t>
+          <t>100%(2/2)</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="J3" t="n">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1.39.12</t>
+          <t>1.38.85</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>29.056</v>
+        <v>28.665</v>
       </c>
       <c r="O3" t="n">
-        <v>23.855</v>
+        <v>23.655</v>
       </c>
       <c r="P3" t="n">
-        <v>23.939</v>
+        <v>24.038</v>
       </c>
       <c r="Q3" t="n">
-        <v>23.229</v>
+        <v>24.168</v>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>29.075</v>
+        <v>28.417</v>
       </c>
       <c r="U3" t="n">
-        <v>23.908</v>
+        <v>23.495</v>
       </c>
       <c r="V3" t="n">
-        <v>24.056</v>
+        <v>24.018</v>
       </c>
       <c r="W3" t="n">
-        <v>23.344</v>
+        <v>24.147</v>
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>52.983</v>
+        <v>51.912</v>
       </c>
       <c r="AA3" t="n">
-        <v>47.4</v>
+        <v>48.165</v>
       </c>
       <c r="AB3" t="n">
-        <v>47.4</v>
+        <v>48.165</v>
       </c>
       <c r="AC3" t="n">
-        <v>100.383</v>
+        <v>100.077</v>
       </c>
       <c r="AD3" t="n">
-        <v>16.41</v>
+        <v>18.42</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>9-8-7-2</t>
+          <t>3-3-1-2</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>留後追趕</t>
+          <t>前置貼欄</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>留後追趕 (中檔, 頭段排名8)</t>
+          <t>前置貼欄 (內檔, 頭段排名3)</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2024_K223</t>
+          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2021_G476</t>
         </is>
       </c>
     </row>
@@ -8093,37 +8123,37 @@
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
-        <v>28.412</v>
+        <v>28.315</v>
       </c>
       <c r="U4" t="n">
-        <v>24.099</v>
+        <v>24.017</v>
       </c>
       <c r="V4" t="n">
-        <v>24.101</v>
+        <v>24.019</v>
       </c>
       <c r="W4" t="n">
-        <v>23.918</v>
+        <v>23.837</v>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>52.511</v>
+        <v>52.332</v>
       </c>
       <c r="AA4" t="n">
-        <v>48.019</v>
+        <v>47.856</v>
       </c>
       <c r="AB4" t="n">
-        <v>48.019</v>
+        <v>47.856</v>
       </c>
       <c r="AC4" t="n">
-        <v>100.53</v>
+        <v>100.188</v>
       </c>
       <c r="AD4" t="n">
-        <v>13.93</v>
+        <v>16.06</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3-6-4-3</t>
+          <t>2-7-4-3</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -8133,7 +8163,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>中置守位 (外檔, 頭段排名6)</t>
+          <t>中置守位 (外檔, 頭段排名7)</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -8209,33 +8239,33 @@
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>29.018</v>
+        <v>28.919</v>
       </c>
       <c r="U5" t="n">
-        <v>23.469</v>
+        <v>23.39</v>
       </c>
       <c r="V5" t="n">
-        <v>24.187</v>
+        <v>24.105</v>
       </c>
       <c r="W5" t="n">
-        <v>24.006</v>
+        <v>23.925</v>
       </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>52.487</v>
+        <v>52.309</v>
       </c>
       <c r="AA5" t="n">
-        <v>48.193</v>
+        <v>48.03</v>
       </c>
       <c r="AB5" t="n">
-        <v>48.193</v>
+        <v>48.03</v>
       </c>
       <c r="AC5" t="n">
-        <v>100.68</v>
+        <v>100.339</v>
       </c>
       <c r="AD5" t="n">
-        <v>11.78</v>
+        <v>13.32</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -8325,37 +8355,37 @@
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="n">
-        <v>28.664</v>
+        <v>28.567</v>
       </c>
       <c r="U6" t="n">
-        <v>23.392</v>
+        <v>23.313</v>
       </c>
       <c r="V6" t="n">
-        <v>24.523</v>
+        <v>24.441</v>
       </c>
       <c r="W6" t="n">
-        <v>24.276</v>
+        <v>24.194</v>
       </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
-        <v>52.056</v>
+        <v>51.88</v>
       </c>
       <c r="AA6" t="n">
-        <v>48.799</v>
+        <v>48.635</v>
       </c>
       <c r="AB6" t="n">
-        <v>48.799</v>
+        <v>48.635</v>
       </c>
       <c r="AC6" t="n">
-        <v>100.855</v>
+        <v>100.515</v>
       </c>
       <c r="AD6" t="n">
-        <v>9.699999999999999</v>
+        <v>10.72</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4-3-3-5</t>
+          <t>4-2-3-5</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -8365,7 +8395,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>前置守位 (中檔, 頭段排名3)</t>
+          <t>前置守位 (中檔, 頭段排名2)</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
@@ -8387,91 +8417,91 @@
         <v>1650</v>
       </c>
       <c r="D7" t="n">
+        <v>12</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>大數據</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>田泰安</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>姚本輝</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>30%(3/10)</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>45</v>
+      </c>
+      <c r="J7" t="n">
+        <v>121</v>
+      </c>
+      <c r="K7" t="n">
         <v>8</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>上浦福旺</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>鍾易禮 (-2)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>沈集成</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>38%(3/8)</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>54</v>
-      </c>
-      <c r="J7" t="n">
-        <v>130</v>
-      </c>
-      <c r="K7" t="n">
-        <v>9</v>
-      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1.39.43</t>
+          <t>1.39.59</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>28.646</v>
+        <v>28.798</v>
       </c>
       <c r="O7" t="n">
-        <v>23.499</v>
+        <v>23.507</v>
       </c>
       <c r="P7" t="n">
-        <v>24.289</v>
+        <v>24.418</v>
       </c>
       <c r="Q7" t="n">
-        <v>24.083</v>
+        <v>23.94</v>
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="n">
-        <v>28.795</v>
+        <v>28.814</v>
       </c>
       <c r="U7" t="n">
-        <v>23.606</v>
+        <v>23.514</v>
       </c>
       <c r="V7" t="n">
-        <v>24.429</v>
+        <v>24.4</v>
       </c>
       <c r="W7" t="n">
-        <v>24.222</v>
+        <v>23.921</v>
       </c>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
-        <v>52.401</v>
+        <v>52.328</v>
       </c>
       <c r="AA7" t="n">
-        <v>48.651</v>
+        <v>48.321</v>
       </c>
       <c r="AB7" t="n">
-        <v>48.651</v>
+        <v>48.321</v>
       </c>
       <c r="AC7" t="n">
-        <v>101.052</v>
+        <v>100.649</v>
       </c>
       <c r="AD7" t="n">
-        <v>7.78</v>
+        <v>9.08</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5-4-6-6</t>
+          <t>7-6-7-6</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -8481,12 +8511,12 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>中置守位 (外檔, 頭段排名4)</t>
+          <t>中置守位 (中檔, 頭段排名6)</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2025_L102</t>
+          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2022_H230</t>
         </is>
       </c>
     </row>
@@ -8503,91 +8533,91 @@
         <v>1650</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>大數據</t>
+          <t>上浦福旺</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>潘明輝</t>
+          <t>鍾易禮 (-2)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>姚本輝</t>
+          <t>沈集成</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>17%(3/18)</t>
+          <t>38%(3/8)</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="J8" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1.39.59</t>
+          <t>1.39.43</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>28.798</v>
+        <v>28.646</v>
       </c>
       <c r="O8" t="n">
-        <v>23.507</v>
+        <v>23.499</v>
       </c>
       <c r="P8" t="n">
-        <v>24.418</v>
+        <v>24.289</v>
       </c>
       <c r="Q8" t="n">
-        <v>23.94</v>
+        <v>24.083</v>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="n">
-        <v>28.989</v>
+        <v>28.697</v>
       </c>
       <c r="U8" t="n">
-        <v>23.657</v>
+        <v>23.526</v>
       </c>
       <c r="V8" t="n">
-        <v>24.548</v>
+        <v>24.346</v>
       </c>
       <c r="W8" t="n">
-        <v>24.066</v>
+        <v>24.14</v>
       </c>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="n">
-        <v>52.646</v>
+        <v>52.223</v>
       </c>
       <c r="AA8" t="n">
-        <v>48.614</v>
+        <v>48.486</v>
       </c>
       <c r="AB8" t="n">
-        <v>48.614</v>
+        <v>48.486</v>
       </c>
       <c r="AC8" t="n">
-        <v>101.26</v>
+        <v>100.709</v>
       </c>
       <c r="AD8" t="n">
-        <v>6.17</v>
+        <v>8.43</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>7-7-8-7</t>
+          <t>5-4-6-7</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -8597,12 +8627,12 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>中置守位 (中檔, 頭段排名7)</t>
+          <t>中置守位 (外檔, 頭段排名4)</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2022_H230</t>
+          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2025_L102</t>
         </is>
       </c>
     </row>
@@ -8673,33 +8703,33 @@
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="n">
-        <v>27.946</v>
+        <v>27.852</v>
       </c>
       <c r="U9" t="n">
-        <v>23.437</v>
+        <v>23.358</v>
       </c>
       <c r="V9" t="n">
-        <v>25.062</v>
+        <v>24.978</v>
       </c>
       <c r="W9" t="n">
-        <v>25.846</v>
+        <v>25.759</v>
       </c>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="n">
-        <v>51.383</v>
+        <v>51.21</v>
       </c>
       <c r="AA9" t="n">
-        <v>50.908</v>
+        <v>50.737</v>
       </c>
       <c r="AB9" t="n">
-        <v>50.908</v>
+        <v>50.737</v>
       </c>
       <c r="AC9" t="n">
-        <v>102.291</v>
+        <v>101.947</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -8789,33 +8819,33 @@
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="n">
-        <v>28.802</v>
+        <v>28.705</v>
       </c>
       <c r="U10" t="n">
-        <v>24.532</v>
+        <v>24.449</v>
       </c>
       <c r="V10" t="n">
-        <v>25.331</v>
+        <v>25.246</v>
       </c>
       <c r="W10" t="n">
-        <v>23.947</v>
+        <v>23.866</v>
       </c>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="n">
-        <v>53.334</v>
+        <v>53.154</v>
       </c>
       <c r="AA10" t="n">
-        <v>49.278</v>
+        <v>49.112</v>
       </c>
       <c r="AB10" t="n">
-        <v>49.278</v>
+        <v>49.112</v>
       </c>
       <c r="AC10" t="n">
-        <v>102.612</v>
+        <v>102.266</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -8900,7 +8930,9 @@
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
+      <c r="AD11" t="n">
+        <v>0.55</v>
+      </c>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
@@ -8972,7 +9004,9 @@
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
+      <c r="AD12" t="n">
+        <v>0.55</v>
+      </c>
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
@@ -9044,7 +9078,9 @@
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
+      <c r="AD13" t="n">
+        <v>0.55</v>
+      </c>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
@@ -9305,31 +9341,31 @@
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>12.518</v>
+        <v>12.475</v>
       </c>
       <c r="U2" t="n">
-        <v>20.79</v>
+        <v>20.72</v>
       </c>
       <c r="V2" t="n">
-        <v>22.591</v>
+        <v>22.514</v>
       </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>33.308</v>
+        <v>33.195</v>
       </c>
       <c r="AA2" t="n">
-        <v>43.381</v>
+        <v>43.234</v>
       </c>
       <c r="AB2" t="n">
-        <v>43.381</v>
+        <v>43.234</v>
       </c>
       <c r="AC2" t="n">
-        <v>55.899</v>
+        <v>55.709</v>
       </c>
       <c r="AD2" t="n">
-        <v>55.17</v>
+        <v>53.87</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -9417,31 +9453,31 @@
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>12.551</v>
+        <v>12.509</v>
       </c>
       <c r="U3" t="n">
-        <v>20.859</v>
+        <v>20.788</v>
       </c>
       <c r="V3" t="n">
-        <v>23.169</v>
+        <v>23.091</v>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>33.41</v>
+        <v>33.297</v>
       </c>
       <c r="AA3" t="n">
-        <v>44.028</v>
+        <v>43.879</v>
       </c>
       <c r="AB3" t="n">
-        <v>44.028</v>
+        <v>43.879</v>
       </c>
       <c r="AC3" t="n">
-        <v>56.579</v>
+        <v>56.388</v>
       </c>
       <c r="AD3" t="n">
-        <v>12.68</v>
+        <v>12.35</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -9529,31 +9565,31 @@
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
-        <v>12.539</v>
+        <v>12.496</v>
       </c>
       <c r="U4" t="n">
-        <v>20.977</v>
+        <v>20.906</v>
       </c>
       <c r="V4" t="n">
-        <v>23.206</v>
+        <v>23.127</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>33.516</v>
+        <v>33.402</v>
       </c>
       <c r="AA4" t="n">
-        <v>44.183</v>
+        <v>44.033</v>
       </c>
       <c r="AB4" t="n">
-        <v>44.183</v>
+        <v>44.033</v>
       </c>
       <c r="AC4" t="n">
-        <v>56.722</v>
+        <v>56.529</v>
       </c>
       <c r="AD4" t="n">
-        <v>9.31</v>
+        <v>9.09</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -9641,31 +9677,31 @@
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>13.152</v>
+        <v>13.108</v>
       </c>
       <c r="U5" t="n">
-        <v>21.82</v>
+        <v>21.746</v>
       </c>
       <c r="V5" t="n">
-        <v>21.824</v>
+        <v>21.75</v>
       </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>34.972</v>
+        <v>34.854</v>
       </c>
       <c r="AA5" t="n">
-        <v>43.644</v>
+        <v>43.496</v>
       </c>
       <c r="AB5" t="n">
-        <v>43.644</v>
+        <v>43.496</v>
       </c>
       <c r="AC5" t="n">
-        <v>56.796</v>
+        <v>56.604</v>
       </c>
       <c r="AD5" t="n">
-        <v>7.93</v>
+        <v>7.73</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -9753,31 +9789,31 @@
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="n">
-        <v>12.896</v>
+        <v>12.852</v>
       </c>
       <c r="U6" t="n">
-        <v>21.567</v>
+        <v>21.494</v>
       </c>
       <c r="V6" t="n">
-        <v>22.375</v>
+        <v>22.299</v>
       </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
-        <v>34.463</v>
+        <v>34.346</v>
       </c>
       <c r="AA6" t="n">
-        <v>43.942</v>
+        <v>43.793</v>
       </c>
       <c r="AB6" t="n">
-        <v>43.942</v>
+        <v>43.793</v>
       </c>
       <c r="AC6" t="n">
-        <v>56.838</v>
+        <v>56.645</v>
       </c>
       <c r="AD6" t="n">
-        <v>7.24</v>
+        <v>7.07</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -9865,31 +9901,31 @@
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="n">
-        <v>12.808</v>
+        <v>12.764</v>
       </c>
       <c r="U7" t="n">
-        <v>21.289</v>
+        <v>21.217</v>
       </c>
       <c r="V7" t="n">
-        <v>22.851</v>
+        <v>22.774</v>
       </c>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
-        <v>34.097</v>
+        <v>33.981</v>
       </c>
       <c r="AA7" t="n">
-        <v>44.14</v>
+        <v>43.991</v>
       </c>
       <c r="AB7" t="n">
-        <v>44.14</v>
+        <v>43.991</v>
       </c>
       <c r="AC7" t="n">
-        <v>56.948</v>
+        <v>56.755</v>
       </c>
       <c r="AD7" t="n">
-        <v>5.71</v>
+        <v>5.57</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -9977,31 +10013,31 @@
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="n">
-        <v>12.772</v>
+        <v>12.729</v>
       </c>
       <c r="U8" t="n">
-        <v>21.419</v>
+        <v>21.346</v>
       </c>
       <c r="V8" t="n">
-        <v>23.252</v>
+        <v>23.173</v>
       </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="n">
-        <v>34.191</v>
+        <v>34.075</v>
       </c>
       <c r="AA8" t="n">
-        <v>44.671</v>
+        <v>44.519</v>
       </c>
       <c r="AB8" t="n">
-        <v>44.671</v>
+        <v>44.519</v>
       </c>
       <c r="AC8" t="n">
-        <v>57.443</v>
+        <v>57.248</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -10090,7 +10126,9 @@
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
+      <c r="AD9" t="n">
+        <v>0.8</v>
+      </c>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
@@ -10162,7 +10200,9 @@
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
+      <c r="AD10" t="n">
+        <v>0.8</v>
+      </c>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
@@ -10234,7 +10274,9 @@
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
+      <c r="AD11" t="n">
+        <v>0.8</v>
+      </c>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
@@ -10495,31 +10537,31 @@
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>23.602</v>
+        <v>23.522</v>
       </c>
       <c r="U2" t="n">
-        <v>22.721</v>
+        <v>22.644</v>
       </c>
       <c r="V2" t="n">
-        <v>23.011</v>
+        <v>22.933</v>
       </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>46.323</v>
+        <v>46.166</v>
       </c>
       <c r="AA2" t="n">
-        <v>45.732</v>
+        <v>45.577</v>
       </c>
       <c r="AB2" t="n">
-        <v>45.732</v>
+        <v>45.577</v>
       </c>
       <c r="AC2" t="n">
-        <v>69.334</v>
+        <v>69.099</v>
       </c>
       <c r="AD2" t="n">
-        <v>25.28</v>
+        <v>24.54</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -10607,31 +10649,31 @@
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>24.392</v>
+        <v>24.309</v>
       </c>
       <c r="U3" t="n">
-        <v>22.56</v>
+        <v>22.483</v>
       </c>
       <c r="V3" t="n">
-        <v>22.471</v>
+        <v>22.394</v>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>46.952</v>
+        <v>46.792</v>
       </c>
       <c r="AA3" t="n">
-        <v>45.031</v>
+        <v>44.877</v>
       </c>
       <c r="AB3" t="n">
-        <v>45.031</v>
+        <v>44.877</v>
       </c>
       <c r="AC3" t="n">
-        <v>69.423</v>
+        <v>69.18600000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>22.51</v>
+        <v>21.91</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -10719,31 +10761,31 @@
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
-        <v>23.981</v>
+        <v>23.899</v>
       </c>
       <c r="U4" t="n">
-        <v>22.749</v>
+        <v>22.672</v>
       </c>
       <c r="V4" t="n">
-        <v>22.898</v>
+        <v>22.82</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>46.73</v>
+        <v>46.571</v>
       </c>
       <c r="AA4" t="n">
-        <v>45.647</v>
+        <v>45.492</v>
       </c>
       <c r="AB4" t="n">
-        <v>45.647</v>
+        <v>45.492</v>
       </c>
       <c r="AC4" t="n">
-        <v>69.628</v>
+        <v>69.39100000000001</v>
       </c>
       <c r="AD4" t="n">
-        <v>17.23</v>
+        <v>16.76</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -10831,31 +10873,31 @@
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>24.135</v>
+        <v>24.053</v>
       </c>
       <c r="U5" t="n">
-        <v>22.562</v>
+        <v>22.486</v>
       </c>
       <c r="V5" t="n">
-        <v>23.05</v>
+        <v>22.971</v>
       </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>46.697</v>
+        <v>46.539</v>
       </c>
       <c r="AA5" t="n">
-        <v>45.612</v>
+        <v>45.457</v>
       </c>
       <c r="AB5" t="n">
-        <v>45.612</v>
+        <v>45.457</v>
       </c>
       <c r="AC5" t="n">
-        <v>69.747</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>14.76</v>
+        <v>14.35</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -10943,31 +10985,31 @@
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="n">
-        <v>24.251</v>
+        <v>24.168</v>
       </c>
       <c r="U6" t="n">
-        <v>22.577</v>
+        <v>22.5</v>
       </c>
       <c r="V6" t="n">
-        <v>23.196</v>
+        <v>23.117</v>
       </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
-        <v>46.828</v>
+        <v>46.668</v>
       </c>
       <c r="AA6" t="n">
-        <v>45.773</v>
+        <v>45.617</v>
       </c>
       <c r="AB6" t="n">
-        <v>45.773</v>
+        <v>45.617</v>
       </c>
       <c r="AC6" t="n">
-        <v>70.024</v>
+        <v>69.785</v>
       </c>
       <c r="AD6" t="n">
-        <v>10.29</v>
+        <v>10.02</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -11055,31 +11097,31 @@
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="n">
-        <v>25.005</v>
+        <v>24.92</v>
       </c>
       <c r="U7" t="n">
-        <v>22.485</v>
+        <v>22.409</v>
       </c>
       <c r="V7" t="n">
-        <v>23.059</v>
+        <v>22.982</v>
       </c>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
-        <v>47.49</v>
+        <v>47.329</v>
       </c>
       <c r="AA7" t="n">
-        <v>45.544</v>
+        <v>45.391</v>
       </c>
       <c r="AB7" t="n">
-        <v>45.544</v>
+        <v>45.391</v>
       </c>
       <c r="AC7" t="n">
-        <v>70.54900000000001</v>
+        <v>70.31100000000001</v>
       </c>
       <c r="AD7" t="n">
-        <v>5.19</v>
+        <v>5.04</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -11167,31 +11209,31 @@
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="n">
-        <v>24.559</v>
+        <v>24.476</v>
       </c>
       <c r="U8" t="n">
-        <v>22.635</v>
+        <v>22.558</v>
       </c>
       <c r="V8" t="n">
-        <v>23.74</v>
+        <v>23.66</v>
       </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="n">
-        <v>47.194</v>
+        <v>47.034</v>
       </c>
       <c r="AA8" t="n">
-        <v>46.375</v>
+        <v>46.218</v>
       </c>
       <c r="AB8" t="n">
-        <v>46.375</v>
+        <v>46.218</v>
       </c>
       <c r="AC8" t="n">
-        <v>70.934</v>
+        <v>70.694</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.14</v>
+        <v>3.06</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -11279,31 +11321,31 @@
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="n">
-        <v>24.017</v>
+        <v>23.936</v>
       </c>
       <c r="U9" t="n">
-        <v>22.538</v>
+        <v>22.462</v>
       </c>
       <c r="V9" t="n">
-        <v>24.9</v>
+        <v>24.816</v>
       </c>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="n">
-        <v>46.555</v>
+        <v>46.398</v>
       </c>
       <c r="AA9" t="n">
-        <v>47.438</v>
+        <v>47.278</v>
       </c>
       <c r="AB9" t="n">
-        <v>47.438</v>
+        <v>47.278</v>
       </c>
       <c r="AC9" t="n">
-        <v>71.455</v>
+        <v>71.214</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -11348,7 +11390,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>潘明輝</t>
+          <t>梁家俊</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -11358,7 +11400,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>22%(7/32)</t>
+          <t>34%(10/29)</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -11388,7 +11430,9 @@
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
+      <c r="AD10" t="n">
+        <v>0.7</v>
+      </c>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
@@ -11460,7 +11504,9 @@
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
+      <c r="AD11" t="n">
+        <v>0.7</v>
+      </c>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
@@ -11532,7 +11578,9 @@
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
+      <c r="AD12" t="n">
+        <v>0.7</v>
+      </c>
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
@@ -11604,7 +11652,9 @@
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
+      <c r="AD13" t="n">
+        <v>0.7</v>
+      </c>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
@@ -11867,33 +11917,33 @@
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>27.924</v>
+        <v>27.829</v>
       </c>
       <c r="U2" t="n">
-        <v>23.859</v>
+        <v>23.778</v>
       </c>
       <c r="V2" t="n">
-        <v>23.8</v>
+        <v>23.719</v>
       </c>
       <c r="W2" t="n">
-        <v>23.392</v>
+        <v>23.312</v>
       </c>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>51.783</v>
+        <v>51.607</v>
       </c>
       <c r="AA2" t="n">
-        <v>47.192</v>
+        <v>47.031</v>
       </c>
       <c r="AB2" t="n">
-        <v>47.192</v>
+        <v>47.031</v>
       </c>
       <c r="AC2" t="n">
-        <v>98.97499999999999</v>
+        <v>98.63800000000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>34.73</v>
+        <v>38.69</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -11929,102 +11979,106 @@
         <v>1650</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>凡凡有餘</t>
+          <t>爆笑</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>布浩榮</t>
+          <t>黃寶妮 (-7)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>沈集成</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>告東尼</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>67%(2/3)</t>
+        </is>
+      </c>
       <c r="I3" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J3" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1.38.85</t>
+          <t>1.38.55</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>28.533</v>
+        <v>28.64</v>
       </c>
       <c r="O3" t="n">
-        <v>23.948</v>
+        <v>23.884</v>
       </c>
       <c r="P3" t="n">
-        <v>23.647</v>
+        <v>23.947</v>
       </c>
       <c r="Q3" t="n">
-        <v>23.299</v>
+        <v>23.761</v>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>28.569</v>
+        <v>28.284</v>
       </c>
       <c r="U3" t="n">
-        <v>23.95</v>
+        <v>23.652</v>
       </c>
       <c r="V3" t="n">
-        <v>23.577</v>
+        <v>23.777</v>
       </c>
       <c r="W3" t="n">
-        <v>23.229</v>
+        <v>23.592</v>
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>52.519</v>
+        <v>51.936</v>
       </c>
       <c r="AA3" t="n">
-        <v>46.806</v>
+        <v>47.369</v>
       </c>
       <c r="AB3" t="n">
-        <v>46.806</v>
+        <v>47.369</v>
       </c>
       <c r="AC3" t="n">
-        <v>99.325</v>
+        <v>99.30500000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>22.13</v>
+        <v>15.59</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>6-5-3-2</t>
+          <t>4-4-2-2</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>中置守位</t>
+          <t>前置貼欄</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>中置守位 (中檔, 頭段排名5)</t>
+          <t>前置貼欄 (內檔, 頭段排名4)</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2023_J364</t>
+          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2023_J079</t>
         </is>
       </c>
     </row>
@@ -12041,106 +12095,102 @@
         <v>1650</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>爆笑</t>
+          <t>凡凡有餘</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>黃寶妮 (-7)</t>
+          <t>布浩榮</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>告東尼</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>67%(2/3)</t>
-        </is>
-      </c>
+          <t>沈集成</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J4" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1.38.55</t>
+          <t>1.38.85</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>28.64</v>
+        <v>28.533</v>
       </c>
       <c r="O4" t="n">
-        <v>23.884</v>
+        <v>23.948</v>
       </c>
       <c r="P4" t="n">
-        <v>23.947</v>
+        <v>23.647</v>
       </c>
       <c r="Q4" t="n">
-        <v>23.761</v>
+        <v>23.299</v>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
-        <v>28.381</v>
+        <v>28.569</v>
       </c>
       <c r="U4" t="n">
-        <v>23.733</v>
+        <v>23.95</v>
       </c>
       <c r="V4" t="n">
-        <v>23.858</v>
+        <v>23.577</v>
       </c>
       <c r="W4" t="n">
-        <v>23.673</v>
+        <v>23.229</v>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>52.114</v>
+        <v>52.519</v>
       </c>
       <c r="AA4" t="n">
-        <v>47.531</v>
+        <v>46.806</v>
       </c>
       <c r="AB4" t="n">
-        <v>47.531</v>
+        <v>46.806</v>
       </c>
       <c r="AC4" t="n">
-        <v>99.645</v>
+        <v>99.325</v>
       </c>
       <c r="AD4" t="n">
-        <v>14.66</v>
+        <v>15.17</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>4-4-2-3</t>
+          <t>6-6-4-3</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>前置貼欄</t>
+          <t>中置守位</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>前置貼欄 (內檔, 頭段排名4)</t>
+          <t>中置守位 (中檔, 頭段排名6)</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2023_J079</t>
+          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2023_J364</t>
         </is>
       </c>
     </row>
@@ -12157,106 +12207,106 @@
         <v>1650</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>雙星報喜</t>
+          <t>瑪瑙</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>班德禮</t>
+          <t>梁家俊</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>呂健威</t>
+          <t>羅富全</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>25%(1/4)</t>
+          <t>34%(10/29)</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="J5" t="n">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="K5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1.39.83</t>
+          <t>1.39.02</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>28.85</v>
+        <v>28.737</v>
       </c>
       <c r="O5" t="n">
-        <v>24.18</v>
+        <v>23.84</v>
       </c>
       <c r="P5" t="n">
-        <v>23.34</v>
+        <v>23.953</v>
       </c>
       <c r="Q5" t="n">
-        <v>23.46</v>
+        <v>23.33</v>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>28.999</v>
+        <v>28.81</v>
       </c>
       <c r="U5" t="n">
-        <v>24.306</v>
+        <v>23.869</v>
       </c>
       <c r="V5" t="n">
-        <v>23.471</v>
+        <v>23.951</v>
       </c>
       <c r="W5" t="n">
-        <v>23.591</v>
+        <v>23.328</v>
       </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>53.305</v>
+        <v>52.679</v>
       </c>
       <c r="AA5" t="n">
-        <v>47.062</v>
+        <v>47.279</v>
       </c>
       <c r="AB5" t="n">
-        <v>47.062</v>
+        <v>47.279</v>
       </c>
       <c r="AC5" t="n">
-        <v>100.367</v>
+        <v>99.958</v>
       </c>
       <c r="AD5" t="n">
-        <v>5.78</v>
+        <v>6.4</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>10-10-7-4</t>
+          <t>7-8-8-4</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>留後追趕</t>
+          <t>中置守位</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>留後追趕 (中檔, 頭段排名10)</t>
+          <t>中置守位 (外檔, 頭段排名8)</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2024_K126</t>
+          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2021_G306</t>
         </is>
       </c>
     </row>
@@ -12273,106 +12323,106 @@
         <v>1650</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>翠兒威威</t>
+          <t>雙星報喜</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>周俊樂 (-2)</t>
+          <t>班德禮</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>巫偉傑</t>
+          <t>呂健威</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>20%(6/30)</t>
+          <t>25%(1/4)</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="J6" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="K6" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1.38.82</t>
+          <t>1.39.83</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>28.185</v>
+        <v>28.85</v>
       </c>
       <c r="O6" t="n">
-        <v>23.871</v>
+        <v>24.18</v>
       </c>
       <c r="P6" t="n">
-        <v>23.767</v>
+        <v>23.34</v>
       </c>
       <c r="Q6" t="n">
-        <v>23.905</v>
+        <v>23.46</v>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="n">
-        <v>28.528</v>
+        <v>28.901</v>
       </c>
       <c r="U6" t="n">
-        <v>24.084</v>
+        <v>24.224</v>
       </c>
       <c r="V6" t="n">
-        <v>23.886</v>
+        <v>23.391</v>
       </c>
       <c r="W6" t="n">
-        <v>24.025</v>
+        <v>23.512</v>
       </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
-        <v>52.612</v>
+        <v>53.125</v>
       </c>
       <c r="AA6" t="n">
-        <v>47.911</v>
+        <v>46.903</v>
       </c>
       <c r="AB6" t="n">
-        <v>47.911</v>
+        <v>46.903</v>
       </c>
       <c r="AC6" t="n">
-        <v>100.523</v>
+        <v>100.028</v>
       </c>
       <c r="AD6" t="n">
-        <v>4.73</v>
+        <v>5.82</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5-6-5-5</t>
+          <t>10-10-7-5</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>中置守位</t>
+          <t>留後追趕</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>中置守位 (外檔, 頭段排名6)</t>
+          <t>留後追趕 (中檔, 頭段排名10)</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2024_K084</t>
+          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2024_K126</t>
         </is>
       </c>
     </row>
@@ -12389,91 +12439,91 @@
         <v>1650</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>瑪瑙</t>
+          <t>翠兒威威</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>潘明輝</t>
+          <t>周俊樂 (-2)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>羅富全</t>
+          <t>巫偉傑</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>22%(7/32)</t>
+          <t>20%(6/30)</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="J7" t="n">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="K7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1.39.02</t>
+          <t>1.38.82</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>28.737</v>
+        <v>28.185</v>
       </c>
       <c r="O7" t="n">
-        <v>23.84</v>
+        <v>23.871</v>
       </c>
       <c r="P7" t="n">
-        <v>23.953</v>
+        <v>23.767</v>
       </c>
       <c r="Q7" t="n">
-        <v>23.33</v>
+        <v>23.905</v>
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="n">
-        <v>28.981</v>
+        <v>28.432</v>
       </c>
       <c r="U7" t="n">
-        <v>24.01</v>
+        <v>24.002</v>
       </c>
       <c r="V7" t="n">
-        <v>24.093</v>
+        <v>23.806</v>
       </c>
       <c r="W7" t="n">
-        <v>23.466</v>
+        <v>23.944</v>
       </c>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
-        <v>52.991</v>
+        <v>52.434</v>
       </c>
       <c r="AA7" t="n">
-        <v>47.559</v>
+        <v>47.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>47.559</v>
+        <v>47.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>100.55</v>
+        <v>100.184</v>
       </c>
       <c r="AD7" t="n">
-        <v>4.57</v>
+        <v>4.71</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>9-8-9-6</t>
+          <t>5-5-5-6</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -12483,12 +12533,12 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>中置守位 (外檔, 頭段排名8)</t>
+          <t>中置守位 (外檔, 頭段排名5)</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2021_G306</t>
+          <t>https://racing.hkjc.com/zh-hk/local/information/horse?horseid=HK_2024_K084</t>
         </is>
       </c>
     </row>
@@ -12559,37 +12609,37 @@
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="n">
-        <v>28.948</v>
+        <v>28.85</v>
       </c>
       <c r="U8" t="n">
-        <v>23.818</v>
+        <v>23.737</v>
       </c>
       <c r="V8" t="n">
-        <v>24.238</v>
+        <v>24.156</v>
       </c>
       <c r="W8" t="n">
-        <v>23.687</v>
+        <v>23.607</v>
       </c>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="n">
-        <v>52.766</v>
+        <v>52.587</v>
       </c>
       <c r="AA8" t="n">
-        <v>47.925</v>
+        <v>47.763</v>
       </c>
       <c r="AB8" t="n">
-        <v>47.925</v>
+        <v>47.763</v>
       </c>
       <c r="AC8" t="n">
-        <v>100.691</v>
+        <v>100.35</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.81</v>
+        <v>3.75</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>8-7-8-7</t>
+          <t>9-7-9-7</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -12675,37 +12725,37 @@
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="n">
-        <v>27.822</v>
+        <v>27.729</v>
       </c>
       <c r="U9" t="n">
-        <v>23.816</v>
+        <v>23.736</v>
       </c>
       <c r="V9" t="n">
-        <v>24.489</v>
+        <v>24.407</v>
       </c>
       <c r="W9" t="n">
-        <v>24.588</v>
+        <v>24.506</v>
       </c>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="n">
-        <v>51.638</v>
+        <v>51.465</v>
       </c>
       <c r="AA9" t="n">
-        <v>49.077</v>
+        <v>48.913</v>
       </c>
       <c r="AB9" t="n">
-        <v>49.077</v>
+        <v>48.913</v>
       </c>
       <c r="AC9" t="n">
-        <v>100.715</v>
+        <v>100.378</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.7</v>
+        <v>3.61</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1-1-4-8</t>
+          <t>1-1-3-8</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -12791,33 +12841,33 @@
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="n">
-        <v>28.217</v>
+        <v>28.122</v>
       </c>
       <c r="U10" t="n">
-        <v>23.706</v>
+        <v>23.625</v>
       </c>
       <c r="V10" t="n">
-        <v>24.675</v>
+        <v>24.591</v>
       </c>
       <c r="W10" t="n">
-        <v>24.46</v>
+        <v>24.377</v>
       </c>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="n">
-        <v>51.923</v>
+        <v>51.747</v>
       </c>
       <c r="AA10" t="n">
-        <v>49.135</v>
+        <v>48.968</v>
       </c>
       <c r="AB10" t="n">
-        <v>49.135</v>
+        <v>48.968</v>
       </c>
       <c r="AC10" t="n">
-        <v>101.058</v>
+        <v>100.715</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -12907,47 +12957,47 @@
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="n">
-        <v>28.92</v>
+        <v>28.823</v>
       </c>
       <c r="U11" t="n">
-        <v>24.071</v>
+        <v>23.99</v>
       </c>
       <c r="V11" t="n">
-        <v>24.345</v>
+        <v>24.263</v>
       </c>
       <c r="W11" t="n">
-        <v>23.883</v>
+        <v>23.803</v>
       </c>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="n">
-        <v>52.991</v>
+        <v>52.813</v>
       </c>
       <c r="AA11" t="n">
-        <v>48.228</v>
+        <v>48.066</v>
       </c>
       <c r="AB11" t="n">
-        <v>48.228</v>
+        <v>48.066</v>
       </c>
       <c r="AC11" t="n">
-        <v>101.219</v>
+        <v>100.879</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>7-8-10-10</t>
+          <t>8-9-10-10</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>包廂跟前</t>
+          <t>留後追趕</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>包廂跟前 (內檔, 頭段排名8)</t>
+          <t>留後追趕 (內檔, 頭段排名9)</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
@@ -13023,33 +13073,33 @@
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="n">
-        <v>29.809</v>
+        <v>29.708</v>
       </c>
       <c r="U12" t="n">
-        <v>24.257</v>
+        <v>24.175</v>
       </c>
       <c r="V12" t="n">
-        <v>24.12</v>
+        <v>24.038</v>
       </c>
       <c r="W12" t="n">
-        <v>23.188</v>
+        <v>23.11</v>
       </c>
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="n">
-        <v>54.066</v>
+        <v>53.883</v>
       </c>
       <c r="AA12" t="n">
-        <v>47.308</v>
+        <v>47.148</v>
       </c>
       <c r="AB12" t="n">
-        <v>47.308</v>
+        <v>47.148</v>
       </c>
       <c r="AC12" t="n">
-        <v>101.374</v>
+        <v>101.031</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -13134,7 +13184,9 @@
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
+      <c r="AD13" t="n">
+        <v>0.67</v>
+      </c>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
